--- a/backend/vetrix_invoices.xlsx
+++ b/backend/vetrix_invoices.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="فاکتورها" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'فاکتورها'!$A$1:$M$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +57,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,121 +433,297 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Customer</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>شماره</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>نوع</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>طرف‌حساب</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>جمع جزء</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>تخفیف</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>مالیات</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>حمل</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>مبلغ نهایی</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>تسویه‌شده</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>باقی‌مانده</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ارز</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 21:32:44</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>buy</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>سعید</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>20000</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>final</t>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>unpaid</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18 17:36:12</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>sale</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>سینا</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>20000</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>final</t>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>unpaid</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 06:57:41</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>sale</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>سینا</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>40000</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>final</t>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>unpaid</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 07:53:03</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>sale</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>سعید</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>600000</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>final</t>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>unpaid</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>IRR</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>